--- a/output/audit_debug_report.xlsx
+++ b/output/audit_debug_report.xlsx
@@ -19,7 +19,7 @@
     <t>Error</t>
   </si>
   <si>
-    <t>Scheme 140088 not found</t>
+    <t>Scheme 149758 not found</t>
   </si>
 </sst>
 </file>
